--- a/Team-Data/2011-12/3-21-2011-12.xlsx
+++ b/Team-Data/2011-12/3-21-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.574</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I2" t="n">
         <v>35.8</v>
       </c>
       <c r="J2" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L2" t="n">
         <v>7.5</v>
@@ -694,73 +761,73 @@
         <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P2" t="n">
         <v>20.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.728</v>
+        <v>0.724</v>
       </c>
       <c r="R2" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S2" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U2" t="n">
         <v>21.7</v>
       </c>
       <c r="V2" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X2" t="n">
         <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="AA2" t="n">
         <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC2" t="n">
         <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
         <v>19</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -769,13 +836,13 @@
         <v>14</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ2" t="n">
         <v>25</v>
@@ -784,7 +851,7 @@
         <v>25</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>24</v>
@@ -793,19 +860,19 @@
         <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>22</v>
@@ -814,7 +881,7 @@
         <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>22</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
         <v>21</v>
@@ -954,7 +1021,7 @@
         <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -975,22 +1042,22 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-13.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1166,7 +1233,7 @@
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.796</v>
+        <v>0.792</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
@@ -1234,31 +1301,31 @@
         <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
         <v>15.8</v>
       </c>
       <c r="P5" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
         <v>13.7</v>
       </c>
       <c r="S5" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T5" t="n">
         <v>46.2</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V5" t="n">
         <v>14</v>
@@ -1273,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
         <v>17.8</v>
@@ -1282,7 +1349,7 @@
         <v>97.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1303,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
         <v>5</v>
@@ -1315,13 +1382,13 @@
         <v>19</v>
       </c>
       <c r="AN5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
         <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
@@ -1330,16 +1397,16 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1348,10 +1415,10 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.386</v>
+        <v>0.395</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I6" t="n">
         <v>34.9</v>
       </c>
       <c r="J6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K6" t="n">
         <v>0.428</v>
@@ -1419,37 +1486,37 @@
         <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.704</v>
+        <v>0.703</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S6" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="T6" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
       <c r="U6" t="n">
         <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y6" t="n">
         <v>6.3</v>
@@ -1458,16 +1525,16 @@
         <v>20.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1479,19 +1546,19 @@
         <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
         <v>16</v>
@@ -1500,10 +1567,10 @@
         <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1512,16 +1579,16 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>19</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
         <v>16</v>
@@ -1539,7 +1606,7 @@
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
         <v>27</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1598,10 +1665,10 @@
         <v>7.5</v>
       </c>
       <c r="M7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O7" t="n">
         <v>15.6</v>
@@ -1610,43 +1677,43 @@
         <v>20.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S7" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T7" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X7" t="n">
         <v>5.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
         <v>19.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
         <v>2</v>
@@ -1655,22 +1722,22 @@
         <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK7" t="n">
         <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,31 +1746,31 @@
         <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>3</v>
@@ -1715,16 +1782,16 @@
         <v>2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
         <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>0.553</v>
+        <v>0.543</v>
       </c>
       <c r="H8" t="n">
         <v>48.9</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.469</v>
+        <v>0.466</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="O8" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P8" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="R8" t="n">
         <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T8" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X8" t="n">
         <v>5.2</v>
@@ -1819,49 +1886,49 @@
         <v>6.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
       <c r="AC8" t="n">
         <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1876,16 +1943,16 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>5</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="n">
         <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J9" t="n">
         <v>79.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M9" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.329</v>
       </c>
       <c r="O9" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="U9" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="X9" t="n">
         <v>3.9</v>
@@ -2004,28 +2071,28 @@
         <v>19.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>25</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
         <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>13</v>
@@ -2052,22 +2119,22 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU9" t="n">
         <v>26</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
         <v>27</v>
@@ -2079,13 +2146,13 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
         <v>17</v>
       </c>
       <c r="BB9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
         <v>26</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -2117,91 +2184,91 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.432</v>
+        <v>0.419</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K10" t="n">
         <v>0.456</v>
       </c>
       <c r="L10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.388</v>
+        <v>0.385</v>
       </c>
       <c r="O10" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P10" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.765</v>
+        <v>0.763</v>
       </c>
       <c r="R10" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="U10" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V10" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
       </c>
       <c r="X10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
@@ -2213,10 +2280,10 @@
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>4</v>
@@ -2225,22 +2292,22 @@
         <v>6</v>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ10" t="n">
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
         <v>26</v>
@@ -2249,13 +2316,13 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
         <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>4</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
@@ -2410,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2434,22 +2501,22 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
         <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>25</v>
@@ -2613,7 +2680,7 @@
         <v>30</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
@@ -2631,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -2663,55 +2730,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
         <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.578</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J13" t="n">
         <v>81.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L13" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M13" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>12.3</v>
       </c>
       <c r="S13" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T13" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U13" t="n">
         <v>20.7</v>
@@ -2720,49 +2787,49 @@
         <v>13.4</v>
       </c>
       <c r="W13" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X13" t="n">
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
         <v>21.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
         <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
         <v>5</v>
@@ -2777,7 +2844,7 @@
         <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2786,13 +2853,13 @@
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT13" t="n">
         <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV13" t="n">
         <v>3</v>
@@ -2801,10 +2868,10 @@
         <v>13</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ13" t="n">
         <v>25</v>
@@ -2816,7 +2883,7 @@
         <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -2845,43 +2912,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.617</v>
+        <v>0.609</v>
       </c>
       <c r="H14" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I14" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J14" t="n">
         <v>79.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M14" t="n">
         <v>17.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.312</v>
+        <v>0.308</v>
       </c>
       <c r="O14" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P14" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q14" t="n">
         <v>0.754</v>
@@ -2890,7 +2957,7 @@
         <v>11.3</v>
       </c>
       <c r="S14" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T14" t="n">
         <v>45.5</v>
@@ -2899,7 +2966,7 @@
         <v>21.4</v>
       </c>
       <c r="V14" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W14" t="n">
         <v>6.1</v>
@@ -2908,22 +2975,22 @@
         <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>95.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2938,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="AI14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
         <v>24</v>
@@ -2953,19 +3020,19 @@
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP14" t="n">
         <v>9</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>11</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2977,28 +3044,28 @@
         <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -3105,28 +3172,28 @@
         <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
       </c>
       <c r="AG15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH15" t="n">
         <v>9</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>8</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3150,10 +3217,10 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>23</v>
@@ -3168,7 +3235,7 @@
         <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>8.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
@@ -3299,13 +3366,13 @@
         <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3353,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>-0.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
         <v>9</v>
@@ -3493,7 +3560,7 @@
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM17" t="n">
         <v>12</v>
@@ -3502,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3520,13 +3587,13 @@
         <v>21</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV17" t="n">
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
         <v>23</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.479</v>
+        <v>0.489</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
@@ -3591,7 +3658,7 @@
         <v>35.7</v>
       </c>
       <c r="J18" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.436</v>
@@ -3600,28 +3667,28 @@
         <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P18" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0.769</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
         <v>32.1</v>
       </c>
       <c r="T18" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U18" t="n">
         <v>19.4</v>
@@ -3636,7 +3703,7 @@
         <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z18" t="n">
         <v>18.9</v>
@@ -3648,7 +3715,7 @@
         <v>98.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AD18" t="n">
         <v>2</v>
@@ -3657,19 +3724,19 @@
         <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
         <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
         <v>24</v>
@@ -3678,19 +3745,19 @@
         <v>13</v>
       </c>
       <c r="AM18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3702,19 +3769,19 @@
         <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV18" t="n">
         <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ18" t="n">
         <v>8</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.313</v>
+        <v>0.319</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,10 +3840,10 @@
         <v>33.7</v>
       </c>
       <c r="J19" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.424</v>
+        <v>0.426</v>
       </c>
       <c r="L19" t="n">
         <v>8.300000000000001</v>
@@ -3785,28 +3852,28 @@
         <v>23.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.774</v>
       </c>
       <c r="R19" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S19" t="n">
         <v>27.9</v>
       </c>
       <c r="T19" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U19" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="n">
         <v>15.4</v>
@@ -3815,22 +3882,22 @@
         <v>7.3</v>
       </c>
       <c r="X19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
         <v>5.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.5</v>
+        <v>-6.2</v>
       </c>
       <c r="AD19" t="n">
         <v>2</v>
@@ -3851,7 +3918,7 @@
         <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
         <v>29</v>
@@ -3875,22 +3942,22 @@
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="n">
         <v>24</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -3937,58 +4004,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
         <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.239</v>
+        <v>0.244</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J20" t="n">
         <v>79</v>
       </c>
       <c r="K20" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="N20" t="n">
         <v>0.324</v>
       </c>
       <c r="O20" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P20" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="n">
         <v>0.757</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U20" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="V20" t="n">
         <v>15.3</v>
@@ -3997,46 +4064,46 @@
         <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
         <v>18.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
       </c>
       <c r="AF20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>28</v>
@@ -4045,7 +4112,7 @@
         <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -4054,34 +4121,34 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
       </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -4119,106 +4186,106 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.489</v>
+        <v>0.478</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J21" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M21" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O21" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P21" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R21" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S21" t="n">
         <v>30.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V21" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W21" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X21" t="n">
         <v>4.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA21" t="n">
         <v>22.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="n">
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>9</v>
@@ -4227,7 +4294,7 @@
         <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4239,13 +4306,13 @@
         <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU21" t="n">
         <v>22</v>
@@ -4260,7 +4327,7 @@
         <v>25</v>
       </c>
       <c r="AY21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4269,10 +4336,10 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -4301,55 +4368,55 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.745</v>
+        <v>0.739</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J22" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.474</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M22" t="n">
         <v>20.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O22" t="n">
         <v>21.5</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U22" t="n">
         <v>18.3</v>
@@ -4364,7 +4431,7 @@
         <v>7.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
         <v>20.3</v>
@@ -4373,13 +4440,13 @@
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.7</v>
+        <v>102.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>12</v>
@@ -4424,13 +4491,13 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.625</v>
+        <v>0.617</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="J23" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L23" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="O23" t="n">
         <v>15.4</v>
       </c>
       <c r="P23" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
         <v>0.644</v>
@@ -4528,13 +4595,13 @@
         <v>11</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
         <v>43</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
         <v>15.5</v>
@@ -4549,16 +4616,16 @@
         <v>4.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA23" t="n">
         <v>20.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
@@ -4597,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,10 +4673,10 @@
         <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
@@ -4627,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4636,7 +4703,7 @@
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
         <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>0.553</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J24" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M24" t="n">
         <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>0.37</v>
+        <v>0.367</v>
       </c>
       <c r="O24" t="n">
         <v>13.3</v>
@@ -4710,52 +4777,52 @@
         <v>10.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T24" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U24" t="n">
         <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="W24" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y24" t="n">
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="AB24" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG24" t="n">
         <v>11</v>
       </c>
-      <c r="AG24" t="n">
-        <v>12</v>
-      </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>6</v>
@@ -4791,7 +4858,7 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
         <v>8</v>
@@ -4800,22 +4867,22 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
         <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J25" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K25" t="n">
         <v>0.454</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O25" t="n">
         <v>15.6</v>
@@ -4886,28 +4953,28 @@
         <v>20.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V25" t="n">
         <v>14.4</v>
       </c>
       <c r="W25" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y25" t="n">
         <v>4.4</v>
@@ -4916,16 +4983,16 @@
         <v>18.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -4943,13 +5010,13 @@
         <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK25" t="n">
         <v>10</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>17</v>
@@ -4958,28 +5025,28 @@
         <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
         <v>11</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
         <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
         <v>26</v>
@@ -4988,13 +5055,13 @@
         <v>5</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
         <v>7</v>
       </c>
       <c r="BA25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
         <v>21</v>
@@ -5125,7 +5192,7 @@
         <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
@@ -5137,13 +5204,13 @@
         <v>13</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5152,7 +5219,7 @@
         <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
         <v>22</v>
@@ -5161,22 +5228,22 @@
         <v>18</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5304,7 +5371,7 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5319,7 +5386,7 @@
         <v>9</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
@@ -5337,7 +5404,7 @@
         <v>26</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
         <v>27</v>
@@ -5346,7 +5413,7 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>23</v>
@@ -5355,7 +5422,7 @@
         <v>28</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.467</v>
@@ -5423,34 +5490,34 @@
         <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="O28" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P28" t="n">
         <v>21.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R28" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T28" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U28" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V28" t="n">
         <v>13.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X28" t="n">
         <v>4.3</v>
@@ -5459,19 +5526,19 @@
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5489,10 +5556,10 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
         <v>18</v>
@@ -5516,10 +5583,10 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5534,10 +5601,10 @@
         <v>26</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>18</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.319</v>
+        <v>0.326</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J29" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P29" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R29" t="n">
         <v>10.2</v>
@@ -5629,7 +5696,7 @@
         <v>21.1</v>
       </c>
       <c r="V29" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -5641,19 +5708,19 @@
         <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>90.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
@@ -5674,7 +5741,7 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>23</v>
@@ -5683,22 +5750,22 @@
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>27</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>25</v>
@@ -5707,7 +5774,7 @@
         <v>13</v>
       </c>
       <c r="AV29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW29" t="n">
         <v>24</v>
@@ -5722,10 +5789,10 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
@@ -5847,7 +5914,7 @@
         <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
         <v>4</v>
@@ -5856,7 +5923,7 @@
         <v>5</v>
       </c>
       <c r="AK30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -5865,7 +5932,7 @@
         <v>29</v>
       </c>
       <c r="AN30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5883,13 +5950,13 @@
         <v>16</v>
       </c>
       <c r="AT30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
         <v>12</v>
       </c>
       <c r="AV30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5907,7 +5974,7 @@
         <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
         <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0.244</v>
+        <v>0.227</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J31" t="n">
         <v>83.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L31" t="n">
         <v>5.1</v>
@@ -5969,16 +6036,16 @@
         <v>15.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.323</v>
+        <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R31" t="n">
         <v>11.9</v>
@@ -5987,13 +6054,13 @@
         <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W31" t="n">
         <v>8</v>
@@ -6005,34 +6072,34 @@
         <v>4.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA31" t="n">
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ31" t="n">
         <v>4</v>
@@ -6047,40 +6114,40 @@
         <v>21</v>
       </c>
       <c r="AN31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
         <v>19</v>
       </c>
       <c r="AP31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV31" t="n">
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>26</v>
@@ -6089,7 +6156,7 @@
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-21-2011-12</t>
+          <t>2012-03-21</t>
         </is>
       </c>
     </row>
